--- a/diseases/d165/2026-2029.xlsx
+++ b/diseases/d165/2026-2029.xlsx
@@ -2491,7 +2491,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9875,7 +9875,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10277,7 +10277,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12562,7 +12562,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13366,7 +13366,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15249,7 +15249,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15651,7 +15651,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16455,7 +16455,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16857,7 +16857,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18347,7 +18347,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18749,7 +18749,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19151,7 +19151,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19553,7 +19553,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20895,7 +20895,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -21297,7 +21297,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -21699,7 +21699,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -22101,7 +22101,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">

--- a/diseases/d165/2026-2029.xlsx
+++ b/diseases/d165/2026-2029.xlsx
@@ -2491,7 +2491,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9875,7 +9875,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10277,7 +10277,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12562,7 +12562,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13366,7 +13366,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15249,7 +15249,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15651,7 +15651,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16455,7 +16455,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16857,7 +16857,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18347,7 +18347,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18749,7 +18749,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19151,7 +19151,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19553,7 +19553,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20497,16 +20497,16 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O104" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>0.1303707733931069</v>
+        <v>0.1347164658395438</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -20895,7 +20895,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -21297,7 +21297,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -21699,7 +21699,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -22101,7 +22101,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -22649,16 +22649,16 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>0.004345692446436896</v>
+        <v>0.01303707733931069</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -22908,7 +22908,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d165/2026-2029.xlsx
+++ b/diseases/d165/2026-2029.xlsx
@@ -22649,16 +22649,16 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O115" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>0.01303707733931069</v>
+        <v>0.01738276978574758</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -22727,6 +22727,408 @@
       <c r="BC115" t="inlineStr">
         <is>
           <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>9</v>
+      </c>
+      <c r="O116" t="n">
+        <v>9</v>
+      </c>
+      <c r="P116" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0.007351275668091897</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP116" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV116" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA116" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB116" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC116" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>9</v>
+      </c>
+      <c r="O117" t="n">
+        <v>9</v>
+      </c>
+      <c r="P117" t="n">
+        <v>9</v>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>Amoebic dysentery</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Japan NIID amoebic dysentery notifications.</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN117" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP117" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV117" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA117" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB117" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC117" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22763,7 +23165,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -22846,7 +23248,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -22856,7 +23258,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11">
@@ -22876,7 +23278,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
@@ -22908,7 +23310,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>463</v>
+        <v>473</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d165/2026-2029.xlsx
+++ b/diseases/d165/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>9</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1554,9 +1548,6 @@
       <c r="O6" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -1702,9 +1693,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -2249,9 +2237,6 @@
       <c r="P10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2501,7 +2486,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2903,7 +2888,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3305,7 +3290,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3707,7 +3692,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -3854,9 +3839,6 @@
       <c r="O18" t="n">
         <v>6</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4247,9 +4229,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4643,9 +4622,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -5046,7 +5022,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -5193,9 +5169,6 @@
       <c r="O25" t="n">
         <v>2</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.01868976085656669</v>
       </c>
@@ -5992,7 +5965,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6394,7 +6367,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6796,7 +6769,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -6943,9 +6916,6 @@
       <c r="O34" t="n">
         <v>10</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7336,9 +7306,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -7732,9 +7699,6 @@
       <c r="O38" t="n">
         <v>1</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -8135,7 +8099,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN40" t="b">
@@ -8282,9 +8246,6 @@
       <c r="O41" t="n">
         <v>3</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.02803464128485004</v>
       </c>
@@ -9081,7 +9042,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9483,7 +9444,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -9885,7 +9846,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10287,7 +10248,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10434,9 +10395,6 @@
       <c r="O52" t="n">
         <v>7</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10827,9 +10785,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -11223,9 +11178,6 @@
       <c r="O56" t="n">
         <v>2</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -11371,9 +11323,6 @@
       <c r="O57" t="n">
         <v>2</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.01868976085656669</v>
       </c>
@@ -11767,9 +11716,6 @@
       <c r="O59" t="n">
         <v>28</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.1216793885002331</v>
       </c>
@@ -12170,7 +12116,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12572,7 +12518,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -12974,7 +12920,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13376,7 +13322,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -13523,9 +13469,6 @@
       <c r="O68" t="n">
         <v>7</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13916,9 +13859,6 @@
       <c r="O70" t="n">
         <v>1</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.01778809170864137</v>
       </c>
@@ -14312,9 +14252,6 @@
       <c r="O72" t="n">
         <v>3</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.04065810840590128</v>
       </c>
@@ -14460,9 +14397,6 @@
       <c r="O73" t="n">
         <v>5</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.04672440214141673</v>
       </c>
@@ -14856,9 +14790,6 @@
       <c r="O75" t="n">
         <v>26</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0.1129880036073593</v>
       </c>
@@ -15259,7 +15190,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -15661,7 +15592,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16063,7 +15994,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16465,7 +16396,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -16867,7 +16798,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17014,9 +16945,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -17410,9 +17338,6 @@
       <c r="O88" t="n">
         <v>2</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -17558,9 +17483,6 @@
       <c r="O89" t="n">
         <v>1</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.009344880428283346</v>
       </c>
@@ -17954,9 +17876,6 @@
       <c r="O91" t="n">
         <v>30</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.1303707733931069</v>
       </c>
@@ -18105,9 +18024,6 @@
       <c r="P92" t="n">
         <v>15</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.01225212611348649</v>
       </c>
@@ -18357,7 +18273,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -18507,9 +18423,6 @@
       <c r="P94" t="n">
         <v>7</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.005717658852960364</v>
       </c>
@@ -18759,7 +18672,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -18909,9 +18822,6 @@
       <c r="P96" t="n">
         <v>6</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.004900850445394598</v>
       </c>
@@ -19161,7 +19071,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -19311,9 +19221,6 @@
       <c r="P98" t="n">
         <v>4</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.003267233630263065</v>
       </c>
@@ -19563,7 +19470,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -19710,9 +19617,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -20106,9 +20010,6 @@
       <c r="O102" t="n">
         <v>5</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.04672440214141673</v>
       </c>
@@ -20502,9 +20403,6 @@
       <c r="O104" t="n">
         <v>31</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.1347164658395438</v>
       </c>
@@ -20653,9 +20551,6 @@
       <c r="P105" t="n">
         <v>4</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.003267233630263065</v>
       </c>
@@ -20905,7 +20800,7 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN106" t="b">
@@ -21055,9 +20950,6 @@
       <c r="P107" t="n">
         <v>7</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.005717658852960364</v>
       </c>
@@ -21307,7 +21199,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -21457,9 +21349,6 @@
       <c r="P109" t="n">
         <v>4</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.003267233630263065</v>
       </c>
@@ -21709,7 +21598,7 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN110" t="b">
@@ -21859,9 +21748,6 @@
       <c r="P111" t="n">
         <v>4</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.003267233630263065</v>
       </c>
@@ -22111,7 +21997,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -22258,9 +22144,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -22649,16 +22532,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O115" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q115" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R115" t="n">
-        <v>0.01738276978574758</v>
+        <v>0.02607415467862137</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -22805,9 +22685,6 @@
       <c r="P116" t="n">
         <v>9</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.007351275668091897</v>
       </c>
@@ -23057,7 +22934,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -23310,7 +23187,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d165/2026-2029.xlsx
+++ b/diseases/d165/2026-2029.xlsx
@@ -22532,13 +22532,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O115" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R115" t="n">
-        <v>0.02607415467862137</v>
+        <v>0.03911123201793206</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d165/2026-2029.xlsx
+++ b/diseases/d165/2026-2029.xlsx
@@ -10390,10 +10390,10 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O52" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -10546,10 +10546,10 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O53" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -16901,12 +16901,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -16940,22 +16940,19 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
-      </c>
-      <c r="R86" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_CA_ON_PHO_IDTO_AMEBIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -16975,12 +16972,12 @@
       </c>
       <c r="AQ86" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_CA_ON_PHO_IDTO_AMEBIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT86" t="n">
@@ -16988,47 +16985,47 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -17060,12 +17057,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -17099,24 +17096,24 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_CA_ON_PHO_IDTO_AMEBIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_CA_ON_PHO_IDTO_AMEBIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
@@ -17131,7 +17128,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -17146,7 +17143,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD87" t="inlineStr">
@@ -17181,17 +17178,17 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
+          <t>PHO IDTO current-year monthly preliminary amebiasis notifications; confirmed cases only under the July 2026 technical notes.</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -17209,12 +17206,12 @@
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_CA_ON_PHO_IDTO_AMEBIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT87" t="n">
@@ -17222,47 +17219,47 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -17294,12 +17291,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -17333,81 +17330,95 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>0.02710540560393419</v>
+        <v>0</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
       <c r="AT88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -17434,17 +17445,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -17478,29 +17489,104 @@
         </is>
       </c>
       <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN89" t="b">
         <v>1</v>
       </c>
-      <c r="O89" t="n">
-        <v>1</v>
-      </c>
-      <c r="R89" t="n">
-        <v>0.009344880428283346</v>
-      </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
-        </is>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -17513,12 +17599,12 @@
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+          <t>SER_FI_THL_TTR_1290</t>
         </is>
       </c>
       <c r="AT89" t="n">
@@ -17526,47 +17612,47 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -17593,17 +17679,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -17637,170 +17723,81 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O90" t="n">
-        <v>1</v>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>Entamoeba histolytica</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD90" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE90" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF90" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG90" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM Entamoeba histolytica source category.</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN90" t="b">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0.02710540560393419</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ90" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -17832,12 +17829,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -17871,81 +17868,95 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="O91" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="R91" t="n">
-        <v>0.1303707733931069</v>
+        <v>0.009344880428283346</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS91" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
       <c r="AT91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -17972,17 +17983,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -18007,7 +18018,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -18016,31 +18027,103 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="O92" t="n">
-        <v>15</v>
-      </c>
-      <c r="P92" t="n">
-        <v>15</v>
-      </c>
-      <c r="R92" t="n">
-        <v>0.01225212611348649</v>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Entamoeba histolytica</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM Entamoeba histolytica source category.</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN92" t="b">
+        <v>1</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -18059,7 +18142,7 @@
       </c>
       <c r="AS92" t="inlineStr">
         <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
         </is>
       </c>
       <c r="AT92" t="n">
@@ -18072,42 +18155,42 @@
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -18134,17 +18217,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -18169,7 +18252,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -18178,173 +18261,81 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="O93" t="n">
-        <v>15</v>
-      </c>
-      <c r="P93" t="n">
-        <v>15</v>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X93" t="inlineStr">
-        <is>
-          <t>Amoebic dysentery</t>
-        </is>
-      </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD93" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE93" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF93" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG93" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Japan NIID amoebic dysentery notifications.</t>
-        </is>
-      </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN93" t="b">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0.1303707733931069</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ93" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -18406,7 +18397,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -18415,16 +18406,16 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="O94" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="P94" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="R94" t="n">
-        <v>0.005717658852960364</v>
+        <v>0.01225212611348649</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -18568,7 +18559,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -18577,13 +18568,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="O95" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="P95" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
@@ -18805,7 +18796,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -18814,16 +18805,16 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O96" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P96" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R96" t="n">
-        <v>0.004900850445394598</v>
+        <v>0.005717658852960364</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -18967,7 +18958,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -18976,13 +18967,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O97" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P97" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -19204,7 +19195,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -19213,16 +19204,16 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O98" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P98" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R98" t="n">
-        <v>0.003267233630263065</v>
+        <v>0.004900850445394598</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -19366,7 +19357,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -19375,13 +19366,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O99" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P99" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
@@ -19573,12 +19564,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -19603,22 +19594,25 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="P100" t="n">
+        <v>4</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -19627,12 +19621,12 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -19647,12 +19641,12 @@
       </c>
       <c r="AQ100" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT100" t="n">
@@ -19660,47 +19654,47 @@
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19732,12 +19726,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -19762,38 +19756,41 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="P101" t="n">
+        <v>4</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>Amebiasis</t>
+          <t>Amoebic dysentery</t>
         </is>
       </c>
       <c r="Y101" t="inlineStr">
@@ -19803,12 +19800,12 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
@@ -19818,7 +19815,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD101" t="inlineStr">
@@ -19833,7 +19830,7 @@
       </c>
       <c r="AF101" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG101" t="inlineStr">
@@ -19853,12 +19850,12 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
+          <t>Japan NIID amoebic dysentery notifications.</t>
         </is>
       </c>
       <c r="AM101" t="inlineStr">
@@ -19881,12 +19878,12 @@
       </c>
       <c r="AQ101" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT101" t="n">
@@ -19894,47 +19891,47 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19966,12 +19963,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -20005,13 +20002,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>0.04672440214141673</v>
+        <v>0</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -20020,7 +20017,7 @@
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+          <t>SER_FI_THL_TTR_1290</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -20040,12 +20037,12 @@
       </c>
       <c r="AQ102" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+          <t>SER_FI_THL_TTR_1290</t>
         </is>
       </c>
       <c r="AT102" t="n">
@@ -20053,47 +20050,47 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20125,12 +20122,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -20164,29 +20161,29 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+          <t>SER_FI_THL_TTR_1290</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+          <t>SER_FI_THL_TTR_1290</t>
         </is>
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>Entamoeba histolytica</t>
+          <t>Amebiasis</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
@@ -20211,7 +20208,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD103" t="inlineStr">
@@ -20246,17 +20243,17 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM Entamoeba histolytica source category.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
         </is>
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -20274,12 +20271,12 @@
       </c>
       <c r="AQ103" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+          <t>SER_FI_THL_TTR_1290</t>
         </is>
       </c>
       <c r="AT103" t="n">
@@ -20287,47 +20284,47 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20359,12 +20356,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -20398,81 +20395,95 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="O104" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="R104" t="n">
-        <v>0.1347164658395438</v>
+        <v>0.04672440214141673</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
       <c r="AT104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -20499,17 +20510,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -20534,7 +20545,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -20543,31 +20554,103 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O105" t="n">
-        <v>4</v>
-      </c>
-      <c r="P105" t="n">
-        <v>4</v>
-      </c>
-      <c r="R105" t="n">
-        <v>0.003267233630263065</v>
-      </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>5</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>Entamoeba histolytica</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM Entamoeba histolytica source category.</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN105" t="b">
+        <v>1</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -20586,7 +20669,7 @@
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
         </is>
       </c>
       <c r="AT105" t="n">
@@ -20599,42 +20682,42 @@
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -20661,17 +20744,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -20696,7 +20779,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -20705,173 +20788,81 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="O106" t="n">
-        <v>4</v>
-      </c>
-      <c r="P106" t="n">
-        <v>4</v>
-      </c>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V106" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W106" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X106" t="inlineStr">
-        <is>
-          <t>Amoebic dysentery</t>
-        </is>
-      </c>
-      <c r="Y106" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA106" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD106" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE106" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF106" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG106" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Japan NIID amoebic dysentery notifications.</t>
-        </is>
-      </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN106" t="b">
-        <v>1</v>
+        <v>31</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0.1347164658395438</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ106" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -20933,7 +20924,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -20942,16 +20933,16 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O107" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P107" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R107" t="n">
-        <v>0.005717658852960364</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -21095,7 +21086,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -21104,13 +21095,13 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O108" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P108" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U108" t="inlineStr">
         <is>
@@ -21332,7 +21323,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -21341,16 +21332,16 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O109" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P109" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R109" t="n">
-        <v>0.003267233630263065</v>
+        <v>0.005717658852960364</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -21494,7 +21485,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -21503,13 +21494,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O110" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P110" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U110" t="inlineStr">
         <is>
@@ -21731,7 +21722,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -21893,7 +21884,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -22100,12 +22091,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -22130,22 +22121,25 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="P113" t="n">
+        <v>4</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -22154,12 +22148,12 @@
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
@@ -22174,12 +22168,12 @@
       </c>
       <c r="AQ113" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT113" t="n">
@@ -22187,47 +22181,47 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22259,12 +22253,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -22289,38 +22283,41 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O114" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="P114" t="n">
+        <v>4</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>Amebiasis</t>
+          <t>Amoebic dysentery</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
@@ -22330,12 +22327,12 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
@@ -22345,7 +22342,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD114" t="inlineStr">
@@ -22360,7 +22357,7 @@
       </c>
       <c r="AF114" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG114" t="inlineStr">
@@ -22380,12 +22377,12 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
+          <t>Japan NIID amoebic dysentery notifications.</t>
         </is>
       </c>
       <c r="AM114" t="inlineStr">
@@ -22408,12 +22405,12 @@
       </c>
       <c r="AQ114" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT114" t="n">
@@ -22421,47 +22418,47 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22493,12 +22490,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -22532,81 +22529,95 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>0.03911123201793206</v>
+        <v>0</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS115" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
       <c r="AT115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -22633,17 +22644,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -22668,7 +22679,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -22677,31 +22688,103 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>9</v>
-      </c>
-      <c r="P116" t="n">
-        <v>9</v>
-      </c>
-      <c r="R116" t="n">
-        <v>0.007351275668091897</v>
-      </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN116" t="b">
+        <v>1</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -22715,12 +22798,12 @@
       </c>
       <c r="AQ116" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
         <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+          <t>SER_FI_THL_TTR_1290</t>
         </is>
       </c>
       <c r="AT116" t="n">
@@ -22728,47 +22811,47 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -22795,17 +22878,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -22830,7 +22913,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -22844,166 +22927,473 @@
       <c r="O117" t="n">
         <v>9</v>
       </c>
-      <c r="P117" t="n">
+      <c r="R117" t="n">
+        <v>0.03911123201793206</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP117" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr"/>
+      <c r="AT117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV117" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA117" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB117" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC117" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
         <v>9</v>
       </c>
-      <c r="U117" t="inlineStr">
+      <c r="O118" t="n">
+        <v>9</v>
+      </c>
+      <c r="P118" t="n">
+        <v>9</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.007351275668091897</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
         <is>
           <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V117" t="inlineStr">
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP118" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
         <is>
           <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
-      <c r="W117" t="inlineStr">
+      <c r="AT118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV118" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA118" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB118" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC118" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>9</v>
+      </c>
+      <c r="O119" t="n">
+        <v>9</v>
+      </c>
+      <c r="P119" t="n">
+        <v>9</v>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
         <is>
           <t>SRC_JP_NIID</t>
         </is>
       </c>
-      <c r="X117" t="inlineStr">
+      <c r="X119" t="inlineStr">
         <is>
           <t>Amoebic dysentery</t>
         </is>
       </c>
-      <c r="Y117" t="inlineStr">
+      <c r="Y119" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
+      <c r="Z119" t="inlineStr">
         <is>
           <t>notification</t>
         </is>
       </c>
-      <c r="AA117" t="inlineStr">
+      <c r="AA119" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
+      <c r="AB119" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr">
+      <c r="AC119" t="inlineStr">
         <is>
           <t>country:JP:national</t>
         </is>
       </c>
-      <c r="AD117" t="inlineStr">
+      <c r="AD119" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE117" t="inlineStr">
+      <c r="AE119" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF117" t="inlineStr">
+      <c r="AF119" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="AG117" t="inlineStr">
+      <c r="AG119" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH117" t="inlineStr">
+      <c r="AH119" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI117" t="inlineStr">
+      <c r="AI119" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ117" t="inlineStr">
+      <c r="AJ119" t="inlineStr">
         <is>
           <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
-      <c r="AK117" t="inlineStr">
+      <c r="AK119" t="inlineStr">
         <is>
           <t>Japan NIID amoebic dysentery notifications.</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
+      <c r="AM119" t="inlineStr">
         <is>
           <t>provisional; raw</t>
         </is>
       </c>
-      <c r="AN117" t="b">
+      <c r="AN119" t="b">
         <v>1</v>
       </c>
-      <c r="AO117" t="inlineStr">
+      <c r="AO119" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP117" t="inlineStr">
+      <c r="AP119" t="inlineStr">
         <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ117" t="inlineStr">
+      <c r="AQ119" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AS117" t="inlineStr">
+      <c r="AS119" t="inlineStr">
         <is>
           <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
-      <c r="AT117" t="n">
+      <c r="AT119" t="n">
         <v>1</v>
       </c>
-      <c r="AU117" t="inlineStr">
+      <c r="AU119" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV117" t="inlineStr">
+      <c r="AV119" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW117" t="inlineStr">
+      <c r="AW119" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX117" t="inlineStr">
+      <c r="AX119" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY117" t="inlineStr">
+      <c r="AY119" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ117" t="inlineStr">
+      <c r="AZ119" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA117" t="inlineStr">
+      <c r="BA119" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB117" t="inlineStr">
+      <c r="BB119" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC117" t="inlineStr">
+      <c r="BC119" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -23125,7 +23515,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10">
@@ -23135,7 +23525,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11">
@@ -23155,7 +23545,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
@@ -23187,7 +23577,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>478</v>
+        <v>485</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d165/2026-2029.xlsx
+++ b/diseases/d165/2026-2029.xlsx
@@ -20788,13 +20788,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O106" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="R106" t="n">
-        <v>0.1347164658395438</v>
+        <v>0.1434078507324176</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -22922,13 +22922,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O117" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R117" t="n">
-        <v>0.03911123201793206</v>
+        <v>0.04345692446436896</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d165/2026-2029.xlsx
+++ b/diseases/d165/2026-2029.xlsx
@@ -23399,6 +23399,405 @@
         </is>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>8</v>
+      </c>
+      <c r="O120" t="n">
+        <v>8</v>
+      </c>
+      <c r="P120" t="n">
+        <v>8</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.00653446726052613</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP120" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV120" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA120" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB120" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC120" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>8</v>
+      </c>
+      <c r="O121" t="n">
+        <v>8</v>
+      </c>
+      <c r="P121" t="n">
+        <v>8</v>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>Amoebic dysentery</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Japan NIID amoebic dysentery notifications.</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN121" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP121" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV121" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA121" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB121" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC121" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23432,7 +23831,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -23515,7 +23914,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10">
@@ -23525,7 +23924,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
@@ -23545,7 +23944,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -23577,7 +23976,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>488</v>
+        <v>496</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d165/2026-2029.xlsx
+++ b/diseases/d165/2026-2029.xlsx
@@ -22529,13 +22529,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -22688,10 +22688,10 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
@@ -23793,6 +23793,405 @@
         </is>
       </c>
       <c r="BC121" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>2</v>
+      </c>
+      <c r="O122" t="n">
+        <v>2</v>
+      </c>
+      <c r="P122" t="n">
+        <v>2</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>2</v>
+      </c>
+      <c r="O123" t="n">
+        <v>2</v>
+      </c>
+      <c r="P123" t="n">
+        <v>2</v>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>Amoebic dysentery</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Japan NIID amoebic dysentery notifications.</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN123" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC123" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -23831,7 +24230,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -23914,7 +24313,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
@@ -23924,7 +24323,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11">
@@ -23944,7 +24343,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13">
@@ -23976,7 +24375,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d165/2026-2029.xlsx
+++ b/diseases/d165/2026-2029.xlsx
@@ -2476,7 +2476,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9434,7 +9434,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13312,7 +13312,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15180,7 +15180,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15582,7 +15582,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16386,7 +16386,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16788,7 +16788,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18653,7 +18653,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19052,7 +19052,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19451,7 +19451,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19850,7 +19850,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21180,7 +21180,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -21579,7 +21579,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -21978,7 +21978,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -22377,7 +22377,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -23314,7 +23314,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -23713,7 +23713,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24112,7 +24112,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">

--- a/diseases/d165/2026-2029.xlsx
+++ b/diseases/d165/2026-2029.xlsx
@@ -2476,7 +2476,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9434,7 +9434,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13312,7 +13312,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15180,7 +15180,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15582,7 +15582,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16386,7 +16386,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16788,7 +16788,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18653,7 +18653,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19052,7 +19052,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19451,7 +19451,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19850,7 +19850,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21180,7 +21180,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -21579,7 +21579,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -21978,7 +21978,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -22377,7 +22377,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -23314,7 +23314,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -23713,7 +23713,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24112,7 +24112,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">

--- a/diseases/d165/2026-2029.xlsx
+++ b/diseases/d165/2026-2029.xlsx
@@ -2476,7 +2476,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9434,7 +9434,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13312,7 +13312,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15180,7 +15180,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15582,7 +15582,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16386,7 +16386,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16788,7 +16788,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18653,7 +18653,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19052,7 +19052,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19451,7 +19451,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19850,7 +19850,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21180,7 +21180,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -21579,7 +21579,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -21978,7 +21978,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -22377,7 +22377,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -23314,7 +23314,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -23713,7 +23713,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24112,7 +24112,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">

--- a/diseases/d165/2026-2029.xlsx
+++ b/diseases/d165/2026-2029.xlsx
@@ -20356,12 +20356,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -20395,95 +20395,81 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O104" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R104" t="n">
-        <v>0.04672440214141673</v>
+        <v>0.02710540560393419</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
-        </is>
-      </c>
-      <c r="AA104" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ104" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -20510,7 +20496,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -20559,98 +20545,23 @@
       <c r="O105" t="n">
         <v>5</v>
       </c>
+      <c r="R105" t="n">
+        <v>0.04672440214141673</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U105" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
         </is>
       </c>
-      <c r="V105" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
-        </is>
-      </c>
-      <c r="W105" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X105" t="inlineStr">
-        <is>
-          <t>Entamoeba histolytica</t>
-        </is>
-      </c>
-      <c r="Y105" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD105" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE105" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF105" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG105" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM Entamoeba histolytica source category.</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN105" t="b">
-        <v>1</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -20744,17 +20655,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -20788,81 +20699,170 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="O106" t="n">
-        <v>33</v>
-      </c>
-      <c r="R106" t="n">
-        <v>0.1434078507324176</v>
-      </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>Entamoeba histolytica</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM Entamoeba histolytica source category.</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN106" t="b">
+        <v>1</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
       <c r="AT106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -20894,12 +20894,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -20924,7 +20924,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -20933,98 +20933,81 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="O107" t="n">
-        <v>4</v>
-      </c>
-      <c r="P107" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="R107" t="n">
-        <v>0.003267233630263065</v>
+        <v>0.1434078507324176</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA107" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ107" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS107" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -21051,7 +21034,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -21103,98 +21086,23 @@
       <c r="P108" t="n">
         <v>4</v>
       </c>
+      <c r="R108" t="n">
+        <v>0.003267233630263065</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U108" t="inlineStr">
         <is>
           <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V108" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W108" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X108" t="inlineStr">
-        <is>
-          <t>Amoebic dysentery</t>
-        </is>
-      </c>
-      <c r="Y108" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD108" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE108" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF108" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG108" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI108" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Japan NIID amoebic dysentery notifications.</t>
-        </is>
-      </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN108" t="b">
-        <v>1</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -21288,7 +21196,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -21323,7 +21231,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -21332,31 +21240,106 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O109" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P109" t="n">
-        <v>7</v>
-      </c>
-      <c r="R109" t="n">
-        <v>0.005717658852960364</v>
-      </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
           <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>Amoebic dysentery</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Japan NIID amoebic dysentery notifications.</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN109" t="b">
+        <v>1</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -21450,7 +21433,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -21502,98 +21485,23 @@
       <c r="P110" t="n">
         <v>7</v>
       </c>
+      <c r="R110" t="n">
+        <v>0.005717658852960364</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U110" t="inlineStr">
         <is>
           <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W110" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X110" t="inlineStr">
-        <is>
-          <t>Amoebic dysentery</t>
-        </is>
-      </c>
-      <c r="Y110" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD110" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE110" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF110" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG110" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Japan NIID amoebic dysentery notifications.</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN110" t="b">
-        <v>1</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -21687,7 +21595,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -21722,7 +21630,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -21731,31 +21639,106 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O111" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P111" t="n">
-        <v>4</v>
-      </c>
-      <c r="R111" t="n">
-        <v>0.003267233630263065</v>
-      </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>7</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
           <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>Amoebic dysentery</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Japan NIID amoebic dysentery notifications.</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN111" t="b">
+        <v>1</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -21849,7 +21832,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -21901,98 +21884,23 @@
       <c r="P112" t="n">
         <v>4</v>
       </c>
+      <c r="R112" t="n">
+        <v>0.003267233630263065</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U112" t="inlineStr">
         <is>
           <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W112" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>Amoebic dysentery</t>
-        </is>
-      </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD112" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE112" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF112" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG112" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Japan NIID amoebic dysentery notifications.</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN112" t="b">
-        <v>1</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -22086,7 +21994,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -22121,7 +22029,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -22138,23 +22046,98 @@
       <c r="P113" t="n">
         <v>4</v>
       </c>
-      <c r="R113" t="n">
-        <v>0.003267233630263065</v>
-      </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U113" t="inlineStr">
         <is>
           <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>Amoebic dysentery</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Japan NIID amoebic dysentery notifications.</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN113" t="b">
+        <v>1</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -22248,7 +22231,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -22300,98 +22283,23 @@
       <c r="P114" t="n">
         <v>4</v>
       </c>
+      <c r="R114" t="n">
+        <v>0.003267233630263065</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U114" t="inlineStr">
         <is>
           <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V114" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W114" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X114" t="inlineStr">
-        <is>
-          <t>Amoebic dysentery</t>
-        </is>
-      </c>
-      <c r="Y114" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD114" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE114" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF114" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG114" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Japan NIID amoebic dysentery notifications.</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN114" t="b">
-        <v>1</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -22485,17 +22393,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -22520,38 +22428,116 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N115" t="n">
+        <v>4</v>
+      </c>
+      <c r="O115" t="n">
+        <v>4</v>
+      </c>
+      <c r="P115" t="n">
+        <v>4</v>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>Amoebic dysentery</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD115" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Japan NIID amoebic dysentery notifications.</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN115" t="b">
         <v>1</v>
       </c>
-      <c r="O115" t="n">
-        <v>1</v>
-      </c>
-      <c r="R115" t="n">
-        <v>0.01778809170864137</v>
-      </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U115" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1290</t>
-        </is>
-      </c>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -22564,12 +22550,12 @@
       </c>
       <c r="AQ115" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT115" t="n">
@@ -22577,47 +22563,47 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22644,7 +22630,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -22693,98 +22679,23 @@
       <c r="O116" t="n">
         <v>1</v>
       </c>
+      <c r="R116" t="n">
+        <v>0.01778809170864137</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U116" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1290</t>
         </is>
       </c>
-      <c r="V116" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1290</t>
-        </is>
-      </c>
-      <c r="W116" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X116" t="inlineStr">
-        <is>
-          <t>Amebiasis</t>
-        </is>
-      </c>
-      <c r="Y116" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD116" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE116" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF116" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG116" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI116" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
-        </is>
-      </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN116" t="b">
-        <v>1</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -22878,17 +22789,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -22922,81 +22833,170 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O117" t="n">
-        <v>10</v>
-      </c>
-      <c r="R117" t="n">
-        <v>0.04345692446436896</v>
-      </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN117" t="b">
+        <v>1</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS117" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
       <c r="AT117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23028,12 +23028,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -23067,98 +23067,81 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O118" t="n">
-        <v>9</v>
-      </c>
-      <c r="P118" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R118" t="n">
-        <v>0.007351275668091897</v>
+        <v>0.04345692446436896</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA118" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ118" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -23185,7 +23168,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -23237,98 +23220,23 @@
       <c r="P119" t="n">
         <v>9</v>
       </c>
+      <c r="R119" t="n">
+        <v>0.007351275668091897</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U119" t="inlineStr">
         <is>
           <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V119" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W119" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X119" t="inlineStr">
-        <is>
-          <t>Amoebic dysentery</t>
-        </is>
-      </c>
-      <c r="Y119" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD119" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE119" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF119" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG119" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Japan NIID amoebic dysentery notifications.</t>
-        </is>
-      </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN119" t="b">
-        <v>1</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -23422,7 +23330,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -23457,7 +23365,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -23466,31 +23374,106 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O120" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P120" t="n">
-        <v>8</v>
-      </c>
-      <c r="R120" t="n">
-        <v>0.00653446726052613</v>
-      </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
           <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>Amoebic dysentery</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Japan NIID amoebic dysentery notifications.</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN120" t="b">
+        <v>1</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -23584,7 +23567,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -23636,98 +23619,23 @@
       <c r="P121" t="n">
         <v>8</v>
       </c>
+      <c r="R121" t="n">
+        <v>0.00653446726052613</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U121" t="inlineStr">
         <is>
           <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V121" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W121" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X121" t="inlineStr">
-        <is>
-          <t>Amoebic dysentery</t>
-        </is>
-      </c>
-      <c r="Y121" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD121" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE121" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF121" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG121" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Japan NIID amoebic dysentery notifications.</t>
-        </is>
-      </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN121" t="b">
-        <v>1</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -23821,7 +23729,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -23856,7 +23764,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -23865,31 +23773,106 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O122" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P122" t="n">
-        <v>2</v>
-      </c>
-      <c r="R122" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
           <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>Amoebic dysentery</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Japan NIID amoebic dysentery notifications.</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN122" t="b">
+        <v>1</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -23983,7 +23966,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -24035,98 +24018,23 @@
       <c r="P123" t="n">
         <v>2</v>
       </c>
+      <c r="R123" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U123" t="inlineStr">
         <is>
           <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V123" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W123" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X123" t="inlineStr">
-        <is>
-          <t>Amoebic dysentery</t>
-        </is>
-      </c>
-      <c r="Y123" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD123" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE123" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF123" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG123" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Japan NIID amoebic dysentery notifications.</t>
-        </is>
-      </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN123" t="b">
-        <v>1</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
@@ -24192,6 +24100,243 @@
         </is>
       </c>
       <c r="BC123" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>2</v>
+      </c>
+      <c r="O124" t="n">
+        <v>2</v>
+      </c>
+      <c r="P124" t="n">
+        <v>2</v>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>Amoebic dysentery</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Japan NIID amoebic dysentery notifications.</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN124" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -24313,7 +24458,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10">
@@ -24323,7 +24468,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11">
@@ -24375,7 +24520,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d165/2026-2029.xlsx
+++ b/diseases/d165/2026-2029.xlsx
@@ -2476,7 +2476,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9434,7 +9434,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13312,7 +13312,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15180,7 +15180,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15582,7 +15582,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16386,7 +16386,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16788,7 +16788,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18653,7 +18653,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19052,7 +19052,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19451,7 +19451,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19850,7 +19850,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21325,7 +21325,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21724,7 +21724,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22123,7 +22123,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -22522,7 +22522,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23459,7 +23459,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -23858,7 +23858,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -24257,7 +24257,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">

--- a/diseases/d165/2026-2029.xlsx
+++ b/diseases/d165/2026-2029.xlsx
@@ -24342,6 +24342,798 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>11</v>
+      </c>
+      <c r="O125" t="n">
+        <v>11</v>
+      </c>
+      <c r="P125" t="n">
+        <v>11</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.00898489248322343</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>11</v>
+      </c>
+      <c r="O126" t="n">
+        <v>11</v>
+      </c>
+      <c r="P126" t="n">
+        <v>11</v>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>Amoebic dysentery</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Japan NIID amoebic dysentery notifications.</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN126" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="AT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD128" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
+        </is>
+      </c>
+      <c r="AM128" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN128" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="AT128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24375,7 +25167,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -24458,7 +25250,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -24468,7 +25260,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11">
@@ -24488,7 +25280,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13">
@@ -24520,7 +25312,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>501</v>
+        <v>512</v>
       </c>
     </row>
     <row r="16">
